--- a/원지가격참조(값).xlsx
+++ b/원지가격참조(값).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\앱프로젝트\Quote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAB2C9D-1977-41EA-9F2F-679DBE9F6F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C951E66-A96A-4B6E-A95B-626277E94643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4092" yWindow="1200" windowWidth="15972" windowHeight="9672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10632" yWindow="252" windowWidth="12084" windowHeight="10368" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="원지가격" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>원지종류</t>
   </si>
@@ -100,6 +100,14 @@
   </si>
   <si>
     <t>평량(g/㎡)</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>적용일자</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.03.04</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -522,7 +530,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -555,6 +563,12 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="36">
@@ -900,13 +914,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{036C729F-9B18-45A0-8AE7-37B630BED733}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="2" max="2" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="34.799999999999997">
+    <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -919,8 +933,11 @@
       <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -928,13 +945,17 @@
         <v>180</v>
       </c>
       <c r="C2" s="2">
-        <v>580000</v>
+        <v>590000</v>
       </c>
       <c r="D2" s="3">
-        <v>104.4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <f>(B2*C2)*1/1000000</f>
+        <v>106.2</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -942,13 +963,14 @@
         <v>180</v>
       </c>
       <c r="C3" s="2">
-        <v>740000</v>
+        <v>800000</v>
       </c>
       <c r="D3" s="3">
-        <v>133.19999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <f t="shared" ref="D3:D20" si="0">(B3*C3)*1/1000000</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,13 +978,14 @@
         <v>180</v>
       </c>
       <c r="C4" s="2">
-        <v>580000</v>
+        <v>590000</v>
       </c>
       <c r="D4" s="3">
-        <v>104.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <f t="shared" si="0"/>
+        <v>106.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -970,13 +993,14 @@
         <v>210</v>
       </c>
       <c r="C5" s="2">
-        <v>630000</v>
+        <v>650000</v>
       </c>
       <c r="D5" s="3">
-        <v>132.30000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <f t="shared" si="0"/>
+        <v>136.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -984,13 +1008,14 @@
         <v>210</v>
       </c>
       <c r="C6" s="2">
-        <v>640000</v>
+        <v>650000</v>
       </c>
       <c r="D6" s="3">
-        <v>134.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <f t="shared" si="0"/>
+        <v>136.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -998,13 +1023,14 @@
         <v>175</v>
       </c>
       <c r="C7" s="2">
-        <v>680000</v>
+        <v>770000</v>
       </c>
       <c r="D7" s="3">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <f t="shared" si="0"/>
+        <v>134.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -1012,13 +1038,14 @@
         <v>225</v>
       </c>
       <c r="C8" s="2">
-        <v>680000</v>
+        <v>770000</v>
       </c>
       <c r="D8" s="3">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <f t="shared" si="0"/>
+        <v>173.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1026,13 +1053,14 @@
         <v>300</v>
       </c>
       <c r="C9" s="2">
-        <v>820000</v>
+        <v>840000</v>
       </c>
       <c r="D9" s="3">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <f t="shared" si="0"/>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -1043,10 +1071,11 @@
         <v>890000</v>
       </c>
       <c r="D10" s="3">
+        <f t="shared" si="0"/>
         <v>195.8</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -1057,10 +1086,11 @@
         <v>890000</v>
       </c>
       <c r="D11" s="3">
+        <f t="shared" si="0"/>
         <v>213.6</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -1068,13 +1098,14 @@
         <v>220</v>
       </c>
       <c r="C12" s="2">
-        <v>640000</v>
+        <v>630000</v>
       </c>
       <c r="D12" s="3">
-        <v>140.80000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <f t="shared" si="0"/>
+        <v>138.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -1082,13 +1113,14 @@
         <v>110</v>
       </c>
       <c r="C13" s="2">
-        <v>500000</v>
+        <v>510000</v>
       </c>
       <c r="D13" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <f t="shared" si="0"/>
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -1096,13 +1128,14 @@
         <v>120</v>
       </c>
       <c r="C14" s="2">
-        <v>490000</v>
+        <v>510000</v>
       </c>
       <c r="D14" s="3">
-        <v>58.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <f t="shared" si="0"/>
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -1110,13 +1143,14 @@
         <v>150</v>
       </c>
       <c r="C15" s="2">
-        <v>500000</v>
+        <v>510000</v>
       </c>
       <c r="D15" s="3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <f t="shared" si="0"/>
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
@@ -1124,10 +1158,11 @@
         <v>160</v>
       </c>
       <c r="C16" s="2">
-        <v>500000</v>
+        <v>520000</v>
       </c>
       <c r="D16" s="3">
-        <v>80</v>
+        <f t="shared" si="0"/>
+        <v>83.2</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1138,10 +1173,11 @@
         <v>180</v>
       </c>
       <c r="C17" s="2">
-        <v>560000</v>
+        <v>570000</v>
       </c>
       <c r="D17" s="3">
-        <v>100.8</v>
+        <f t="shared" si="0"/>
+        <v>102.6</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1152,10 +1188,11 @@
         <v>180</v>
       </c>
       <c r="C18" s="2">
-        <v>480000</v>
+        <v>490000</v>
       </c>
       <c r="D18" s="3">
-        <v>86.4</v>
+        <f t="shared" si="0"/>
+        <v>88.2</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1166,10 +1203,11 @@
         <v>250</v>
       </c>
       <c r="C19" s="2">
-        <v>480000</v>
+        <v>490000</v>
       </c>
       <c r="D19" s="3">
-        <v>120</v>
+        <f t="shared" si="0"/>
+        <v>122.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" thickBot="1">
@@ -1180,10 +1218,11 @@
         <v>200</v>
       </c>
       <c r="C20" s="5">
-        <v>480000</v>
+        <v>490000</v>
       </c>
       <c r="D20" s="6">
-        <v>96</v>
+        <f t="shared" si="0"/>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
